--- a/school_data/sd_2_stage/Здания школ.xlsx
+++ b/school_data/sd_2_stage/Здания школ.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\analysis-of-educational-institutions\global_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\analysis-of-educational-institutions\school_data\sd_2_stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Информация о школах Саратова" sheetId="1" r:id="rId1"/>
     <sheet name="schools" sheetId="2" r:id="rId2"/>
     <sheet name="Лист1" sheetId="3" r:id="rId3"/>
     <sheet name="schools_1_stage" sheetId="4" r:id="rId4"/>
-    <sheet name="schools_2_stage" sheetId="5" r:id="rId5"/>
+    <sheet name="ссылка_госуслуги" sheetId="6" r:id="rId5"/>
+    <sheet name="schools_2_stage" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Информация о школах Саратова'!$A$1:$Y$139</definedName>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7241" uniqueCount="1783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7504" uniqueCount="1892">
   <si>
     <t>ID</t>
   </si>
@@ -5375,6 +5376,333 @@
   </si>
   <si>
     <t>Учителя_Тональность</t>
+  </si>
+  <si>
+    <t>ссылка на госуслуги</t>
+  </si>
+  <si>
+    <t>https://gim2-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://ntg-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim87-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim58-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sh-80-lastochkino-saratov-r64.gosweb.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school66vavilov.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic56-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sch46-saratov.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gel-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://ftl-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk14-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk16-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lgn-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk10-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk94-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://raskovo.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk5-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk97-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://kleshevka.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://mourpkg.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school23saratov.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk7-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://solaris.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk11-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk77-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk52-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk102-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk82-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk76-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school63-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk95-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk67-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk8-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic24-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk90-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk1-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk91-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://aviator-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk51-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk21-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk59-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school55sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk84-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school100sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shkola106-saratov64.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shkola-72-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk22-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk6-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk43-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk17-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sargymn1.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk71-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://ivolgino.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gymn3sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk18-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim31-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk54-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic2-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sc40sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk41-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk101-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic47-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk44-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school70-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk48-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk103-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk60-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk61-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://zvezda-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk57-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk86-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://unikum64.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk64-sar.gosuslugi.ru/svedeniya-ob-obrazovatelnoy-organizatsii/osnovnye-svedeniya/</t>
+  </si>
+  <si>
+    <t>https://shk38-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk73-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic53-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lyceum62.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim108-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic15-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim7-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk49-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://moulpn.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk26-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk45-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sh-int3-saratov-r64.gosweb.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk237-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk78-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim5-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://inlic-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic50-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim75-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic37-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk2-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim34-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lmi-sar.gosuslugi.ru/svedeniya-ob-obrazovatelnoy-organizatsii/osnovnye-svedeniya/</t>
+  </si>
+  <si>
+    <t>https://lic3-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic4-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk81-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shk83-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://shkola-internat4.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://school9saratov.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sh-int5-saratov-r64.gosweb.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://gim89-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://korschool2.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic36-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://mbl-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://lic107-sar.gosuslugi.ru/</t>
+  </si>
+  <si>
+    <t>https://sh6-saratov-r64.gosweb.gosuslugi.ru/</t>
   </si>
 </sst>
 </file>
@@ -5851,27 +6179,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y172"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="70.140625" style="11" customWidth="1"/>
-    <col min="3" max="4" width="24.5703125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="70.109375" style="11" customWidth="1"/>
+    <col min="3" max="4" width="24.5546875" style="11" customWidth="1"/>
     <col min="5" max="5" width="18" style="11" customWidth="1"/>
     <col min="6" max="6" width="9" style="2" customWidth="1"/>
     <col min="7" max="7" width="6" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="2" customWidth="1"/>
-    <col min="11" max="14" width="5.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="5.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="2" customWidth="1"/>
+    <col min="11" max="14" width="5.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.33203125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.33203125" style="2" customWidth="1"/>
     <col min="17" max="18" width="13" style="11" customWidth="1"/>
     <col min="19" max="19" width="20" style="11" customWidth="1"/>
-    <col min="20" max="20" width="8.85546875" style="11" customWidth="1"/>
-    <col min="22" max="22" width="15.28515625" style="11" customWidth="1"/>
-    <col min="23" max="25" width="8.85546875" style="11" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="11" customWidth="1"/>
+    <col min="22" max="22" width="15.33203125" style="11" customWidth="1"/>
+    <col min="23" max="25" width="8.88671875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5948,7 +6276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -5998,7 +6326,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -6060,7 +6388,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -6113,7 +6441,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -6169,7 +6497,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -6231,7 +6559,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -6290,7 +6618,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -6352,7 +6680,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
@@ -6408,7 +6736,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -6467,7 +6795,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -6526,7 +6854,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -6589,7 +6917,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -6648,7 +6976,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>157</v>
       </c>
@@ -6710,7 +7038,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -6757,7 +7085,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -6807,7 +7135,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>190</v>
       </c>
@@ -6868,7 +7196,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>198</v>
       </c>
@@ -6926,7 +7254,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>207</v>
       </c>
@@ -6991,7 +7319,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="20" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -7042,7 +7370,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>228</v>
       </c>
@@ -7095,7 +7423,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>235</v>
       </c>
@@ -7160,7 +7488,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>246</v>
       </c>
@@ -7204,7 +7532,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>255</v>
       </c>
@@ -7263,7 +7591,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -7322,7 +7650,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>277</v>
       </c>
@@ -7375,7 +7703,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>286</v>
       </c>
@@ -7431,7 +7759,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>295</v>
       </c>
@@ -7487,7 +7815,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>301</v>
       </c>
@@ -7537,7 +7865,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>310</v>
       </c>
@@ -7590,7 +7918,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>319</v>
       </c>
@@ -7640,7 +7968,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>328</v>
       </c>
@@ -7698,7 +8026,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>337</v>
       </c>
@@ -7757,7 +8085,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="34" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -7811,7 +8139,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>357</v>
       </c>
@@ -7864,7 +8192,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>366</v>
       </c>
@@ -7926,7 +8254,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>377</v>
       </c>
@@ -7985,7 +8313,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>388</v>
       </c>
@@ -8047,7 +8375,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>399</v>
       </c>
@@ -8115,7 +8443,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>410</v>
       </c>
@@ -8177,7 +8505,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>421</v>
       </c>
@@ -8236,7 +8564,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>431</v>
       </c>
@@ -8292,7 +8620,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>442</v>
       </c>
@@ -8354,7 +8682,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>453</v>
       </c>
@@ -8419,7 +8747,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>463</v>
       </c>
@@ -8471,7 +8799,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>473</v>
       </c>
@@ -8533,7 +8861,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>484</v>
       </c>
@@ -8589,7 +8917,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>493</v>
       </c>
@@ -8651,7 +8979,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>504</v>
       </c>
@@ -8701,7 +9029,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>514</v>
       </c>
@@ -8754,7 +9082,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>524</v>
       </c>
@@ -8816,7 +9144,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>535</v>
       </c>
@@ -8878,7 +9206,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>546</v>
       </c>
@@ -8940,7 +9268,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>557</v>
       </c>
@@ -9000,7 +9328,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>564</v>
       </c>
@@ -9068,7 +9396,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>575</v>
       </c>
@@ -9127,7 +9455,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>586</v>
       </c>
@@ -9188,7 +9516,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>597</v>
       </c>
@@ -9244,7 +9572,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>608</v>
       </c>
@@ -9306,7 +9634,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>619</v>
       </c>
@@ -9365,7 +9693,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>630</v>
       </c>
@@ -9427,7 +9755,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>641</v>
       </c>
@@ -9489,7 +9817,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>652</v>
       </c>
@@ -9548,7 +9876,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>663</v>
       </c>
@@ -9610,7 +9938,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>674</v>
       </c>
@@ -9664,7 +9992,7 @@
       <c r="X65" s="9"/>
       <c r="Y65" s="9"/>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>679</v>
       </c>
@@ -9726,7 +10054,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>690</v>
       </c>
@@ -9785,7 +10113,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>699</v>
       </c>
@@ -9844,7 +10172,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>710</v>
       </c>
@@ -9912,7 +10240,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>720</v>
       </c>
@@ -9977,7 +10305,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>731</v>
       </c>
@@ -10042,7 +10370,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>742</v>
       </c>
@@ -10104,7 +10432,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>753</v>
       </c>
@@ -10166,7 +10494,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>764</v>
       </c>
@@ -10228,7 +10556,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>775</v>
       </c>
@@ -10287,7 +10615,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>786</v>
       </c>
@@ -10343,7 +10671,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>797</v>
       </c>
@@ -10405,7 +10733,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>808</v>
       </c>
@@ -10464,7 +10792,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>819</v>
       </c>
@@ -10520,7 +10848,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>828</v>
       </c>
@@ -10579,7 +10907,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>839</v>
       </c>
@@ -10641,7 +10969,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>850</v>
       </c>
@@ -10700,7 +11028,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>858</v>
       </c>
@@ -10762,7 +11090,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>869</v>
       </c>
@@ -10824,7 +11152,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>880</v>
       </c>
@@ -10889,7 +11217,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>891</v>
       </c>
@@ -10951,7 +11279,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>902</v>
       </c>
@@ -11013,7 +11341,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>913</v>
       </c>
@@ -11078,7 +11406,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>924</v>
       </c>
@@ -11140,7 +11468,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>935</v>
       </c>
@@ -11199,7 +11527,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>946</v>
       </c>
@@ -11267,7 +11595,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>957</v>
       </c>
@@ -11329,7 +11657,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="93" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>968</v>
       </c>
@@ -11392,7 +11720,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>979</v>
       </c>
@@ -11451,7 +11779,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>990</v>
       </c>
@@ -11510,7 +11838,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1001</v>
       </c>
@@ -11572,7 +11900,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1012</v>
       </c>
@@ -11634,7 +11962,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1023</v>
       </c>
@@ -11696,7 +12024,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1034</v>
       </c>
@@ -11755,7 +12083,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1045</v>
       </c>
@@ -11817,7 +12145,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1056</v>
       </c>
@@ -11876,7 +12204,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1066</v>
       </c>
@@ -11935,7 +12263,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1077</v>
       </c>
@@ -11991,7 +12319,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="104" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1088</v>
       </c>
@@ -12056,7 +12384,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1099</v>
       </c>
@@ -12115,7 +12443,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1110</v>
       </c>
@@ -12180,7 +12508,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1120</v>
       </c>
@@ -12242,7 +12570,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1131</v>
       </c>
@@ -12292,7 +12620,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>1140</v>
       </c>
@@ -12353,7 +12681,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1151</v>
       </c>
@@ -12412,7 +12740,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1162</v>
       </c>
@@ -12471,7 +12799,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1173</v>
       </c>
@@ -12530,7 +12858,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1183</v>
       </c>
@@ -12592,7 +12920,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1194</v>
       </c>
@@ -12657,7 +12985,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1205</v>
       </c>
@@ -12722,7 +13050,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1216</v>
       </c>
@@ -12787,7 +13115,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
         <v>1227</v>
       </c>
@@ -12849,7 +13177,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1235</v>
       </c>
@@ -12905,7 +13233,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1246</v>
       </c>
@@ -12973,7 +13301,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1257</v>
       </c>
@@ -13032,7 +13360,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1267</v>
       </c>
@@ -13091,7 +13419,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1276</v>
       </c>
@@ -13153,7 +13481,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>1287</v>
       </c>
@@ -13220,7 +13548,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1298</v>
       </c>
@@ -13273,7 +13601,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1309</v>
       </c>
@@ -13332,7 +13660,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1320</v>
       </c>
@@ -13391,7 +13719,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>1331</v>
       </c>
@@ -13456,7 +13784,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1340</v>
       </c>
@@ -13518,7 +13846,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>1351</v>
       </c>
@@ -13589,7 +13917,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1362</v>
       </c>
@@ -13642,7 +13970,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1373</v>
       </c>
@@ -13707,7 +14035,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1384</v>
       </c>
@@ -13769,7 +14097,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1395</v>
       </c>
@@ -13828,7 +14156,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1406</v>
       </c>
@@ -13887,7 +14215,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1416</v>
       </c>
@@ -13946,7 +14274,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>1427</v>
       </c>
@@ -14005,7 +14333,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>1438</v>
       </c>
@@ -14052,7 +14380,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1447</v>
       </c>
@@ -14099,7 +14427,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>1456</v>
       </c>
@@ -14146,7 +14474,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>1465</v>
       </c>
@@ -14193,7 +14521,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>1474</v>
       </c>
@@ -14243,7 +14571,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>1483</v>
       </c>
@@ -14293,7 +14621,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>1492</v>
       </c>
@@ -14346,7 +14674,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>1501</v>
       </c>
@@ -14393,7 +14721,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>1510</v>
       </c>
@@ -14440,7 +14768,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>1519</v>
       </c>
@@ -14493,7 +14821,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>1528</v>
       </c>
@@ -14543,7 +14871,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>1537</v>
       </c>
@@ -14593,7 +14921,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>1546</v>
       </c>
@@ -14646,7 +14974,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1555</v>
       </c>
@@ -14693,7 +15021,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1564</v>
       </c>
@@ -14743,7 +15071,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1573</v>
       </c>
@@ -14796,7 +15124,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1582</v>
       </c>
@@ -14843,7 +15171,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1591</v>
       </c>
@@ -14896,7 +15224,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1600</v>
       </c>
@@ -14949,7 +15277,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1609</v>
       </c>
@@ -15002,7 +15330,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1618</v>
       </c>
@@ -15055,7 +15383,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1627</v>
       </c>
@@ -15108,7 +15436,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1636</v>
       </c>
@@ -15170,7 +15498,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1647</v>
       </c>
@@ -15232,7 +15560,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1658</v>
       </c>
@@ -15282,7 +15610,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1667</v>
       </c>
@@ -15332,7 +15660,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1676</v>
       </c>
@@ -15400,9 +15728,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD135"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15479,7 +15807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -15535,7 +15863,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -15602,7 +15930,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -15660,7 +15988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -15723,7 +16051,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -15790,7 +16118,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -15855,7 +16183,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -15922,7 +16250,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
@@ -15985,7 +16313,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -16050,7 +16378,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -16115,7 +16443,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -16183,7 +16511,7 @@
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -16248,7 +16576,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>157</v>
       </c>
@@ -16315,7 +16643,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -16370,7 +16698,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -16427,7 +16755,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>190</v>
       </c>
@@ -16493,7 +16821,7 @@
       <c r="AC17" s="5"/>
       <c r="AD17" s="5"/>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>198</v>
       </c>
@@ -16556,7 +16884,7 @@
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>207</v>
       </c>
@@ -16626,7 +16954,7 @@
       <c r="AC19" s="5"/>
       <c r="AD19" s="5"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -16682,7 +17010,7 @@
       <c r="AC20" s="5"/>
       <c r="AD20" s="5"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>228</v>
       </c>
@@ -16739,7 +17067,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>235</v>
       </c>
@@ -16808,7 +17136,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>246</v>
       </c>
@@ -16859,7 +17187,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>255</v>
       </c>
@@ -16924,7 +17252,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -16989,7 +17317,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>277</v>
       </c>
@@ -17047,7 +17375,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>286</v>
       </c>
@@ -17107,7 +17435,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>295</v>
       </c>
@@ -17167,7 +17495,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>301</v>
       </c>
@@ -17223,7 +17551,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>310</v>
       </c>
@@ -17281,7 +17609,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>319</v>
       </c>
@@ -17337,7 +17665,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>328</v>
       </c>
@@ -17400,7 +17728,7 @@
       <c r="AC32" s="9"/>
       <c r="AD32" s="9"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>337</v>
       </c>
@@ -17465,7 +17793,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -17524,7 +17852,7 @@
       <c r="AC34" s="9"/>
       <c r="AD34" s="9"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>357</v>
       </c>
@@ -17582,7 +17910,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>366</v>
       </c>
@@ -17649,7 +17977,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>377</v>
       </c>
@@ -17714,7 +18042,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>388</v>
       </c>
@@ -17781,7 +18109,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>399</v>
       </c>
@@ -17852,7 +18180,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>410</v>
       </c>
@@ -17919,7 +18247,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>421</v>
       </c>
@@ -17984,7 +18312,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>431</v>
       </c>
@@ -18047,7 +18375,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>442</v>
       </c>
@@ -18114,7 +18442,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>453</v>
       </c>
@@ -18183,7 +18511,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>463</v>
       </c>
@@ -18242,7 +18570,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>473</v>
       </c>
@@ -18309,7 +18637,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>484</v>
       </c>
@@ -18372,7 +18700,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>493</v>
       </c>
@@ -18439,7 +18767,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>504</v>
       </c>
@@ -18495,7 +18823,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>514</v>
       </c>
@@ -18556,7 +18884,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>524</v>
       </c>
@@ -18623,7 +18951,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>535</v>
       </c>
@@ -18690,7 +19018,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>546</v>
       </c>
@@ -18757,7 +19085,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>557</v>
       </c>
@@ -18822,7 +19150,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>564</v>
       </c>
@@ -18893,7 +19221,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>575</v>
       </c>
@@ -18958,7 +19286,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>586</v>
       </c>
@@ -19019,7 +19347,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>597</v>
       </c>
@@ -19082,7 +19410,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>608</v>
       </c>
@@ -19149,7 +19477,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>619</v>
       </c>
@@ -19214,7 +19542,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>630</v>
       </c>
@@ -19281,7 +19609,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>641</v>
       </c>
@@ -19348,7 +19676,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>652</v>
       </c>
@@ -19413,7 +19741,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>663</v>
       </c>
@@ -19480,7 +19808,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>674</v>
       </c>
@@ -19539,7 +19867,7 @@
       <c r="X65" s="9"/>
       <c r="Y65" s="9"/>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>679</v>
       </c>
@@ -19606,7 +19934,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>690</v>
       </c>
@@ -19671,7 +19999,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>699</v>
       </c>
@@ -19736,7 +20064,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>710</v>
       </c>
@@ -19807,7 +20135,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>720</v>
       </c>
@@ -19876,7 +20204,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>731</v>
       </c>
@@ -19945,7 +20273,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>742</v>
       </c>
@@ -20012,7 +20340,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>753</v>
       </c>
@@ -20079,7 +20407,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>764</v>
       </c>
@@ -20146,7 +20474,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>775</v>
       </c>
@@ -20211,7 +20539,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>786</v>
       </c>
@@ -20274,7 +20602,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>797</v>
       </c>
@@ -20341,7 +20669,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>808</v>
       </c>
@@ -20406,7 +20734,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>819</v>
       </c>
@@ -20469,7 +20797,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>828</v>
       </c>
@@ -20534,7 +20862,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>839</v>
       </c>
@@ -20601,7 +20929,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>850</v>
       </c>
@@ -20662,7 +20990,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>858</v>
       </c>
@@ -20729,7 +21057,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>869</v>
       </c>
@@ -20796,7 +21124,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>880</v>
       </c>
@@ -20865,7 +21193,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>891</v>
       </c>
@@ -20932,7 +21260,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>902</v>
       </c>
@@ -20999,7 +21327,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>913</v>
       </c>
@@ -21068,7 +21396,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>924</v>
       </c>
@@ -21135,7 +21463,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>935</v>
       </c>
@@ -21200,7 +21528,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>946</v>
       </c>
@@ -21271,7 +21599,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>957</v>
       </c>
@@ -21338,7 +21666,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>968</v>
       </c>
@@ -21406,7 +21734,7 @@
       <c r="AC93" s="9"/>
       <c r="AD93" s="9"/>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>979</v>
       </c>
@@ -21471,7 +21799,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>990</v>
       </c>
@@ -21536,7 +21864,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1001</v>
       </c>
@@ -21603,7 +21931,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1012</v>
       </c>
@@ -21670,7 +21998,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1023</v>
       </c>
@@ -21737,7 +22065,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1034</v>
       </c>
@@ -21802,7 +22130,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1045</v>
       </c>
@@ -21869,7 +22197,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1056</v>
       </c>
@@ -21934,7 +22262,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1066</v>
       </c>
@@ -21999,7 +22327,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1077</v>
       </c>
@@ -22062,7 +22390,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1088</v>
       </c>
@@ -22132,7 +22460,7 @@
       <c r="AC104" s="9"/>
       <c r="AD104" s="9"/>
     </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1099</v>
       </c>
@@ -22197,7 +22525,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1110</v>
       </c>
@@ -22266,7 +22594,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1120</v>
       </c>
@@ -22333,7 +22661,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1131</v>
       </c>
@@ -22389,7 +22717,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="109" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>1140</v>
       </c>
@@ -22450,7 +22778,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1151</v>
       </c>
@@ -22515,7 +22843,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1162</v>
       </c>
@@ -22580,7 +22908,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1173</v>
       </c>
@@ -22645,7 +22973,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1183</v>
       </c>
@@ -22712,7 +23040,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1194</v>
       </c>
@@ -22781,7 +23109,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1205</v>
       </c>
@@ -22850,7 +23178,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1216</v>
       </c>
@@ -22919,7 +23247,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
         <v>1227</v>
       </c>
@@ -22986,7 +23314,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1235</v>
       </c>
@@ -23049,7 +23377,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1246</v>
       </c>
@@ -23120,7 +23448,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1257</v>
       </c>
@@ -23185,7 +23513,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1267</v>
       </c>
@@ -23250,7 +23578,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1276</v>
       </c>
@@ -23317,7 +23645,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>1287</v>
       </c>
@@ -23384,7 +23712,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1298</v>
       </c>
@@ -23444,7 +23772,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1309</v>
       </c>
@@ -23509,7 +23837,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1320</v>
       </c>
@@ -23574,7 +23902,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>1331</v>
       </c>
@@ -23639,7 +23967,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1340</v>
       </c>
@@ -23706,7 +24034,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>1351</v>
       </c>
@@ -23779,7 +24107,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1362</v>
       </c>
@@ -23839,7 +24167,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1373</v>
       </c>
@@ -23908,7 +24236,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1384</v>
       </c>
@@ -23975,7 +24303,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1395</v>
       </c>
@@ -24040,7 +24368,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1406</v>
       </c>
@@ -24105,7 +24433,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1416</v>
       </c>
@@ -24181,13 +24509,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="37.28515625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" style="11" customWidth="1"/>
     <col min="19" max="19" width="27" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24264,7 +24592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
@@ -24278,7 +24606,7 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -24293,7 +24621,7 @@
       <c r="P5" s="2"/>
       <c r="S5" s="9"/>
     </row>
-    <row r="9" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10"/>
@@ -24320,7 +24648,7 @@
       <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="5"/>
@@ -24338,7 +24666,7 @@
       <c r="P10" s="2"/>
       <c r="S10" s="9"/>
     </row>
-    <row r="16" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>190</v>
       </c>
@@ -24399,7 +24727,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>228</v>
       </c>
@@ -24456,7 +24784,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>463</v>
       </c>
@@ -24515,7 +24843,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>557</v>
       </c>
@@ -24580,7 +24908,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>674</v>
       </c>
@@ -24639,7 +24967,7 @@
       <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>1227</v>
       </c>
@@ -24706,7 +25034,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>295</v>
       </c>
@@ -24766,7 +25094,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>484</v>
       </c>
@@ -24829,7 +25157,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>410</v>
       </c>
@@ -24896,7 +25224,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="30" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>328</v>
       </c>
@@ -24954,7 +25282,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>190</v>
       </c>
@@ -25001,7 +25329,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>228</v>
       </c>
@@ -25042,7 +25370,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>463</v>
       </c>
@@ -25091,7 +25419,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>557</v>
       </c>
@@ -25142,7 +25470,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>674</v>
       </c>
@@ -25194,9 +25522,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG135"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="87.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -25297,7 +25628,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -25380,7 +25711,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -25475,7 +25806,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -25558,7 +25889,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>101</v>
       </c>
@@ -25650,7 +25981,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>102</v>
       </c>
@@ -25745,7 +26076,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>103</v>
       </c>
@@ -25837,7 +26168,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>104</v>
       </c>
@@ -25932,7 +26263,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>105</v>
       </c>
@@ -26024,7 +26355,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>106</v>
       </c>
@@ -26116,7 +26447,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>107</v>
       </c>
@@ -26211,7 +26542,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>108</v>
       </c>
@@ -26303,7 +26634,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>109</v>
       </c>
@@ -26395,7 +26726,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -26490,7 +26821,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>110</v>
       </c>
@@ -26573,7 +26904,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>111</v>
       </c>
@@ -26659,7 +26990,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>115</v>
       </c>
@@ -26745,7 +27076,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>117</v>
       </c>
@@ -26831,7 +27162,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>12</v>
       </c>
@@ -26923,7 +27254,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>122</v>
       </c>
@@ -27003,7 +27334,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>124</v>
       </c>
@@ -27083,7 +27414,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>13</v>
       </c>
@@ -27178,7 +27509,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>130</v>
       </c>
@@ -27258,7 +27589,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>14</v>
       </c>
@@ -27353,7 +27684,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>15</v>
       </c>
@@ -27445,7 +27776,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>153</v>
       </c>
@@ -27531,7 +27862,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>154</v>
       </c>
@@ -27620,7 +27951,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>155</v>
       </c>
@@ -27709,7 +28040,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>156</v>
       </c>
@@ -27795,7 +28126,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>157</v>
       </c>
@@ -27881,7 +28212,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>158</v>
       </c>
@@ -27961,7 +28292,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>159</v>
       </c>
@@ -28047,7 +28378,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>16</v>
       </c>
@@ -28139,7 +28470,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>160</v>
       </c>
@@ -28222,7 +28553,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>161</v>
       </c>
@@ -28308,7 +28639,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>162</v>
       </c>
@@ -28403,7 +28734,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>163</v>
       </c>
@@ -28498,7 +28829,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>164</v>
       </c>
@@ -28596,7 +28927,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>165</v>
       </c>
@@ -28694,7 +29025,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>167</v>
       </c>
@@ -28789,7 +29120,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>168</v>
       </c>
@@ -28884,7 +29215,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>169</v>
       </c>
@@ -28973,7 +29304,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>17</v>
       </c>
@@ -29068,7 +29399,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>170</v>
       </c>
@@ -29166,7 +29497,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>171</v>
       </c>
@@ -29252,7 +29583,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>173</v>
       </c>
@@ -29347,7 +29678,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>175</v>
       </c>
@@ -29439,7 +29770,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>18</v>
       </c>
@@ -29534,7 +29865,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>19</v>
       </c>
@@ -29617,7 +29948,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2</v>
       </c>
@@ -29706,7 +30037,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>20</v>
       </c>
@@ -29801,7 +30132,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>21</v>
       </c>
@@ -29893,7 +30224,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>22</v>
       </c>
@@ -29988,7 +30319,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>23</v>
       </c>
@@ -30080,7 +30411,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>24</v>
       </c>
@@ -30178,7 +30509,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>25</v>
       </c>
@@ -30270,7 +30601,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>26</v>
       </c>
@@ -30359,7 +30690,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>27</v>
       </c>
@@ -30448,7 +30779,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>28</v>
       </c>
@@ -30543,7 +30874,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>29</v>
       </c>
@@ -30635,7 +30966,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>3</v>
       </c>
@@ -30730,7 +31061,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>30</v>
       </c>
@@ -30825,7 +31156,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>31</v>
       </c>
@@ -30917,7 +31248,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>32</v>
       </c>
@@ -31012,7 +31343,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>33</v>
       </c>
@@ -31095,7 +31426,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>34</v>
       </c>
@@ -31193,7 +31524,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>35</v>
       </c>
@@ -31288,7 +31619,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>36</v>
       </c>
@@ -31380,7 +31711,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>37</v>
       </c>
@@ -31478,7 +31809,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>38</v>
       </c>
@@ -31576,7 +31907,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>39</v>
       </c>
@@ -31671,7 +32002,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>4</v>
       </c>
@@ -31769,7 +32100,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>40</v>
       </c>
@@ -31864,7 +32195,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>41</v>
       </c>
@@ -31959,7 +32290,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>42</v>
       </c>
@@ -32051,7 +32382,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>43</v>
       </c>
@@ -32140,7 +32471,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>44</v>
       </c>
@@ -32235,7 +32566,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>45</v>
       </c>
@@ -32327,7 +32658,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>46</v>
       </c>
@@ -32419,7 +32750,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>47</v>
       </c>
@@ -32511,7 +32842,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>48</v>
       </c>
@@ -32606,7 +32937,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>49</v>
       </c>
@@ -32692,7 +33023,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>5</v>
       </c>
@@ -32787,7 +33118,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>50</v>
       </c>
@@ -32882,7 +33213,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>51</v>
       </c>
@@ -32980,7 +33311,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>52</v>
       </c>
@@ -33075,7 +33406,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>53</v>
       </c>
@@ -33170,7 +33501,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>54</v>
       </c>
@@ -33265,7 +33596,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>55</v>
       </c>
@@ -33360,7 +33691,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>56</v>
       </c>
@@ -33452,7 +33783,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>57</v>
       </c>
@@ -33550,7 +33881,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>58</v>
       </c>
@@ -33645,7 +33976,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>59</v>
       </c>
@@ -33734,7 +34065,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>6</v>
       </c>
@@ -33829,7 +34160,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>60</v>
       </c>
@@ -33921,7 +34252,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>61</v>
       </c>
@@ -34016,7 +34347,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>62</v>
       </c>
@@ -34111,7 +34442,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>63</v>
       </c>
@@ -34203,7 +34534,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>64</v>
       </c>
@@ -34295,7 +34626,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>65</v>
       </c>
@@ -34390,7 +34721,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>66</v>
       </c>
@@ -34485,7 +34816,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>67</v>
       </c>
@@ -34580,7 +34911,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>68</v>
       </c>
@@ -34669,7 +35000,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>69</v>
       </c>
@@ -34761,7 +35092,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>7</v>
       </c>
@@ -34853,7 +35184,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>70</v>
       </c>
@@ -34951,7 +35282,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>71</v>
       </c>
@@ -35046,7 +35377,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>72</v>
       </c>
@@ -35129,7 +35460,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>73</v>
       </c>
@@ -35218,7 +35549,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>74</v>
       </c>
@@ -35307,7 +35638,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>75</v>
       </c>
@@ -35399,7 +35730,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>76</v>
       </c>
@@ -35491,7 +35822,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>77</v>
       </c>
@@ -35586,7 +35917,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>78</v>
       </c>
@@ -35684,7 +36015,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>79</v>
       </c>
@@ -35779,7 +36110,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>8</v>
       </c>
@@ -35874,7 +36205,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>80</v>
       </c>
@@ -35969,7 +36300,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>81</v>
       </c>
@@ -36058,7 +36389,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>82</v>
       </c>
@@ -36156,7 +36487,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>83</v>
       </c>
@@ -36251,7 +36582,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>84</v>
       </c>
@@ -36346,7 +36677,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>85</v>
       </c>
@@ -36438,7 +36769,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>87</v>
       </c>
@@ -36533,7 +36864,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>88</v>
       </c>
@@ -36622,7 +36953,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>89</v>
       </c>
@@ -36714,7 +37045,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>9</v>
       </c>
@@ -36809,7 +37140,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>90</v>
       </c>
@@ -36898,7 +37229,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>91</v>
       </c>
@@ -36993,7 +37324,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>92</v>
       </c>
@@ -37091,7 +37422,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>93</v>
       </c>
@@ -37180,7 +37511,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>94</v>
       </c>
@@ -37275,7 +37606,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>95</v>
       </c>
@@ -37370,7 +37701,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>96</v>
       </c>
@@ -37462,7 +37793,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>97</v>
       </c>
@@ -37554,7 +37885,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>98</v>
       </c>
@@ -37656,19 +37987,1492 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DI135"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C133"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="71.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="34" max="34" width="38.28515625" customWidth="1"/>
-    <col min="41" max="41" width="48.5703125" customWidth="1"/>
-    <col min="105" max="105" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="11"/>
+    <col min="2" max="2" width="100.88671875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>10</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>100</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>101</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>102</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>103</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>104</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>105</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>106</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>107</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="11">
+        <v>108</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="11">
+        <v>109</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="11">
+        <v>11</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="11">
+        <v>110</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="11">
+        <v>111</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="11">
+        <v>115</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="11">
+        <v>117</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="11">
+        <v>12</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="11">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="11">
+        <v>124</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
+        <v>13</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>130</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>14</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>15</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>153</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>154</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
+        <v>155</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>156</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
+        <v>157</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
+        <v>158</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="11">
+        <v>159</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>16</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>160</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
+        <v>161</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
+        <v>162</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
+        <v>163</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="11">
+        <v>164</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="11">
+        <v>165</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="11">
+        <v>167</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="11">
+        <v>168</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="11">
+        <v>169</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="11">
+        <v>17</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="11">
+        <v>170</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="11">
+        <v>171</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="11">
+        <v>173</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="11">
+        <v>175</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="11">
+        <v>18</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="11">
+        <v>19</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="11">
+        <v>2</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
+        <v>20</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="11">
+        <v>21</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="11">
+        <v>22</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="11">
+        <v>23</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="11">
+        <v>24</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="11">
+        <v>25</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="11">
+        <v>26</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="11">
+        <v>27</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="11">
+        <v>28</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="11">
+        <v>29</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="11">
+        <v>3</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="11">
+        <v>30</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="11">
+        <v>31</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="11">
+        <v>32</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="11">
+        <v>33</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="11">
+        <v>34</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="11">
+        <v>35</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="11">
+        <v>36</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="11">
+        <v>37</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="11">
+        <v>38</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="11">
+        <v>39</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="11">
+        <v>4</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="11">
+        <v>40</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>754</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="11">
+        <v>41</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="11">
+        <v>42</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="11">
+        <v>43</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="11">
+        <v>44</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="11">
+        <v>45</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>809</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="11">
+        <v>46</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="11">
+        <v>47</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="11">
+        <v>48</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="11">
+        <v>5</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>859</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="11">
+        <v>50</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="11">
+        <v>51</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="11">
+        <v>52</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="11">
+        <v>53</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
+        <v>54</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>914</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="11">
+        <v>55</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>925</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="11">
+        <v>56</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="11">
+        <v>57</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>947</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="11">
+        <v>58</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>958</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="11">
+        <v>59</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="11">
+        <v>6</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>980</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="11">
+        <v>60</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="11">
+        <v>61</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="11">
+        <v>62</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="11">
+        <v>63</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="11">
+        <v>64</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="11">
+        <v>65</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="11">
+        <v>67</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="11">
+        <v>68</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="11">
+        <v>69</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="11">
+        <v>7</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="11">
+        <v>70</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="11">
+        <v>71</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="11">
+        <v>72</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="11">
+        <v>73</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="11">
+        <v>74</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="11">
+        <v>75</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="11">
+        <v>76</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="11">
+        <v>77</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="11">
+        <v>78</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="11">
+        <v>79</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="11">
+        <v>8</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="11">
+        <v>80</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="11">
+        <v>81</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="11">
+        <v>82</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="11">
+        <v>83</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="11">
+        <v>84</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="11">
+        <v>85</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="11">
+        <v>87</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="11">
+        <v>88</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="11">
+        <v>89</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="11">
+        <v>9</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="11">
+        <v>90</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="11">
+        <v>91</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="11">
+        <v>92</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="11">
+        <v>93</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="11">
+        <v>94</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="11">
+        <v>95</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="11">
+        <v>96</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="11">
+        <v>97</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="11">
+        <v>98</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1"/>
+    <hyperlink ref="C30" r:id="rId2"/>
+    <hyperlink ref="C31" r:id="rId3"/>
+    <hyperlink ref="C32" r:id="rId4"/>
+    <hyperlink ref="C34" r:id="rId5"/>
+    <hyperlink ref="C132" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:DI135"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="71.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="34" max="34" width="38.33203125" customWidth="1"/>
+    <col min="41" max="41" width="48.5546875" customWidth="1"/>
+    <col min="105" max="105" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -38009,7 +39813,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -38308,7 +40112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -38631,7 +40435,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -38942,7 +40746,7 @@
         <v>0.78947368421052633</v>
       </c>
     </row>
-    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -39238,7 +41042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -39561,7 +41365,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -39869,7 +41673,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -40168,7 +41972,7 @@
         <v>0.29411764705882348</v>
       </c>
     </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
@@ -40428,7 +42232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -40736,7 +42540,7 @@
         <v>0.62790697674418605</v>
       </c>
     </row>
-    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -40999,7 +42803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>135</v>
       </c>
@@ -41259,7 +43063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>146</v>
       </c>
@@ -41531,7 +43335,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>157</v>
       </c>
@@ -41818,7 +43622,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>168</v>
       </c>
@@ -42057,7 +43861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -42299,7 +44103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>190</v>
       </c>
@@ -42601,7 +44405,7 @@
         <v>0.69696969696969702</v>
       </c>
     </row>
-    <row r="18" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>198</v>
       </c>
@@ -42867,7 +44671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>207</v>
       </c>
@@ -43151,7 +44955,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="20" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -43231,7 +45035,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="21" spans="1:113" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:113" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>228</v>
       </c>
@@ -43536,7 +45340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>235</v>
       </c>
@@ -43859,7 +45663,7 @@
         <v>0.69230769230769229</v>
       </c>
     </row>
-    <row r="23" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>246</v>
       </c>
@@ -43939,7 +45743,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="24" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>255</v>
       </c>
@@ -44262,7 +46066,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>266</v>
       </c>
@@ -44582,7 +46386,7 @@
         <v>0.1111111111111111</v>
       </c>
     </row>
-    <row r="26" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>277</v>
       </c>
@@ -44836,7 +46640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>286</v>
       </c>
@@ -45081,7 +46885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>295</v>
       </c>
@@ -45386,7 +47190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>301</v>
       </c>
@@ -45640,7 +47444,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="30" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>310</v>
       </c>
@@ -45906,7 +47710,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>319</v>
       </c>
@@ -46154,7 +47958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>328</v>
       </c>
@@ -46456,7 +48260,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>337</v>
       </c>
@@ -46728,7 +48532,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -46979,7 +48783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>357</v>
       </c>
@@ -47245,7 +49049,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>366</v>
       </c>
@@ -47544,7 +49348,7 @@
         <v>0.24444444444444441</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>377</v>
       </c>
@@ -47867,7 +49671,7 @@
         <v>0.31034482758620691</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>388</v>
       </c>
@@ -48181,7 +49985,7 @@
         <v>0.53846153846153844</v>
       </c>
     </row>
-    <row r="39" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>399</v>
       </c>
@@ -48519,7 +50323,7 @@
         <v>0.1891891891891892</v>
       </c>
     </row>
-    <row r="40" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>410</v>
       </c>
@@ -48842,7 +50646,7 @@
         <v>0.35849056603773582</v>
       </c>
     </row>
-    <row r="41" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>421</v>
       </c>
@@ -49165,7 +50969,7 @@
         <v>0.69230769230769229</v>
       </c>
     </row>
-    <row r="42" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>431</v>
       </c>
@@ -49458,7 +51262,7 @@
         <v>0.84615384615384615</v>
       </c>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>442</v>
       </c>
@@ -49757,7 +51561,7 @@
         <v>0.88571428571428568</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>453</v>
       </c>
@@ -50095,7 +51899,7 @@
         <v>0.1785714285714286</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>463</v>
       </c>
@@ -50349,7 +52153,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>473</v>
       </c>
@@ -50660,7 +52464,7 @@
         <v>-0.36842105263157893</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>484</v>
       </c>
@@ -50920,7 +52724,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>493</v>
       </c>
@@ -51219,7 +53023,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="49" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>504</v>
       </c>
@@ -51530,7 +53334,7 @@
         <v>0.76470588235294112</v>
       </c>
     </row>
-    <row r="50" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>514</v>
       </c>
@@ -51859,7 +53663,7 @@
         <v>0.31034482758620691</v>
       </c>
     </row>
-    <row r="51" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>524</v>
       </c>
@@ -52170,7 +53974,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="52" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>535</v>
       </c>
@@ -52490,7 +54294,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="53" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>546</v>
       </c>
@@ -52777,7 +54581,7 @@
         <v>0.53846153846153844</v>
       </c>
     </row>
-    <row r="54" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>557</v>
       </c>
@@ -53097,7 +54901,7 @@
         <v>0.2413793103448276</v>
       </c>
     </row>
-    <row r="55" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>564</v>
       </c>
@@ -53411,7 +55215,7 @@
         <v>0.85185185185185186</v>
       </c>
     </row>
-    <row r="56" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>575</v>
       </c>
@@ -53719,7 +55523,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>586</v>
       </c>
@@ -54024,7 +55828,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="58" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>597</v>
       </c>
@@ -54317,7 +56121,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="59" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>608</v>
       </c>
@@ -54628,7 +56432,7 @@
         <v>0.28205128205128199</v>
       </c>
     </row>
-    <row r="60" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>619</v>
       </c>
@@ -54924,7 +56728,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="61" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>630</v>
       </c>
@@ -55259,7 +57063,7 @@
         <v>0.53488372093023251</v>
       </c>
     </row>
-    <row r="62" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>641</v>
       </c>
@@ -55546,7 +57350,7 @@
         <v>0.72413793103448276</v>
       </c>
     </row>
-    <row r="63" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>652</v>
       </c>
@@ -55842,7 +57646,7 @@
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="64" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>663</v>
       </c>
@@ -56153,7 +57957,7 @@
         <v>0.42105263157894729</v>
       </c>
     </row>
-    <row r="65" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>674</v>
       </c>
@@ -56452,7 +58256,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="66" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>679</v>
       </c>
@@ -56766,7 +58570,7 @@
         <v>0.34883720930232559</v>
       </c>
     </row>
-    <row r="67" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>690</v>
       </c>
@@ -57017,7 +58821,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="68" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>699</v>
       </c>
@@ -57313,7 +59117,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="69" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>710</v>
       </c>
@@ -57639,7 +59443,7 @@
         <v>0.62962962962962965</v>
       </c>
     </row>
-    <row r="70" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>720</v>
       </c>
@@ -57929,7 +59733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>731</v>
       </c>
@@ -58252,7 +60056,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="72" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>742</v>
       </c>
@@ -58566,7 +60370,7 @@
         <v>0.70588235294117652</v>
       </c>
     </row>
-    <row r="73" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>753</v>
       </c>
@@ -58877,7 +60681,7 @@
         <v>-0.15384615384615391</v>
       </c>
     </row>
-    <row r="74" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>764</v>
       </c>
@@ -59188,7 +60992,7 @@
         <v>0.41176470588235292</v>
       </c>
     </row>
-    <row r="75" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>775</v>
       </c>
@@ -59520,7 +61324,7 @@
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>786</v>
       </c>
@@ -59825,7 +61629,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="77" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>797</v>
       </c>
@@ -60148,7 +61952,7 @@
         <v>0.35714285714285721</v>
       </c>
     </row>
-    <row r="78" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>808</v>
       </c>
@@ -60456,7 +62260,7 @@
         <v>0.13043478260869559</v>
       </c>
     </row>
-    <row r="79" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>819</v>
       </c>
@@ -60740,7 +62544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>828</v>
       </c>
@@ -61060,7 +62864,7 @@
         <v>0.61290322580645162</v>
       </c>
     </row>
-    <row r="81" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>839</v>
       </c>
@@ -61383,7 +63187,7 @@
         <v>0.26666666666666672</v>
       </c>
     </row>
-    <row r="82" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>850</v>
       </c>
@@ -61673,7 +63477,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="83" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>858</v>
       </c>
@@ -61996,7 +63800,7 @@
         <v>0.39130434782608697</v>
       </c>
     </row>
-    <row r="84" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>869</v>
       </c>
@@ -62295,7 +64099,7 @@
         <v>0.35483870967741937</v>
       </c>
     </row>
-    <row r="85" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>880</v>
       </c>
@@ -62609,7 +64413,7 @@
         <v>0.81818181818181823</v>
       </c>
     </row>
-    <row r="86" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>891</v>
       </c>
@@ -62920,7 +64724,7 @@
         <v>0.35483870967741937</v>
       </c>
     </row>
-    <row r="87" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>902</v>
       </c>
@@ -63231,7 +65035,7 @@
         <v>0.56521739130434778</v>
       </c>
     </row>
-    <row r="88" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>913</v>
       </c>
@@ -63530,7 +65334,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="89" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>924</v>
       </c>
@@ -63817,7 +65621,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="90" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>935</v>
       </c>
@@ -64125,7 +65929,7 @@
         <v>0.47368421052631582</v>
       </c>
     </row>
-    <row r="91" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>946</v>
       </c>
@@ -64427,7 +66231,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="92" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>957</v>
       </c>
@@ -64714,7 +66518,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="93" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>968</v>
       </c>
@@ -65031,7 +66835,7 @@
         <v>-9.6774193548387094E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>979</v>
       </c>
@@ -65342,7 +67146,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="95" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>990</v>
       </c>
@@ -65662,7 +67466,7 @@
         <v>0.23076923076923081</v>
       </c>
     </row>
-    <row r="96" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1001</v>
       </c>
@@ -65985,7 +67789,7 @@
         <v>0.55555555555555558</v>
       </c>
     </row>
-    <row r="97" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1012</v>
       </c>
@@ -66320,7 +68124,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="98" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1023</v>
       </c>
@@ -66628,7 +68432,7 @@
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="99" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1034</v>
       </c>
@@ -66936,7 +68740,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="100" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1045</v>
       </c>
@@ -67223,7 +69027,7 @@
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="101" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1056</v>
       </c>
@@ -67558,7 +69362,7 @@
         <v>0.39130434782608697</v>
       </c>
     </row>
-    <row r="102" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1066</v>
       </c>
@@ -67845,7 +69649,7 @@
         <v>0.6470588235294118</v>
       </c>
     </row>
-    <row r="103" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1077</v>
       </c>
@@ -68126,7 +69930,7 @@
         <v>0.44444444444444442</v>
       </c>
     </row>
-    <row r="104" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1088</v>
       </c>
@@ -68434,7 +70238,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="105" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1099</v>
       </c>
@@ -68742,7 +70546,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="106" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1110</v>
       </c>
@@ -69056,7 +70860,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="107" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1120</v>
       </c>
@@ -69367,7 +71171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1131</v>
       </c>
@@ -69654,7 +71458,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="109" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>1140</v>
       </c>
@@ -69947,7 +71751,7 @@
         <v>0.47368421052631582</v>
       </c>
     </row>
-    <row r="110" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1151</v>
       </c>
@@ -70228,7 +72032,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="111" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1162</v>
       </c>
@@ -70548,7 +72352,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="112" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1173</v>
       </c>
@@ -70844,7 +72648,7 @@
         <v>0.76470588235294112</v>
       </c>
     </row>
-    <row r="113" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1183</v>
       </c>
@@ -71155,7 +72959,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="114" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1194</v>
       </c>
@@ -71457,7 +73261,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="115" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1205</v>
       </c>
@@ -71780,7 +73584,7 @@
         <v>0.35294117647058831</v>
       </c>
     </row>
-    <row r="116" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1216</v>
       </c>
@@ -72103,7 +73907,7 @@
         <v>0.15789473684210531</v>
       </c>
     </row>
-    <row r="117" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>1227</v>
       </c>
@@ -72414,7 +74218,7 @@
         <v>0.69696969696969702</v>
       </c>
     </row>
-    <row r="118" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1235</v>
       </c>
@@ -72719,7 +74523,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="119" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1246</v>
       </c>
@@ -73033,7 +74837,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="120" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1257</v>
       </c>
@@ -73368,7 +75172,7 @@
         <v>-5.8823529411764712E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1267</v>
       </c>
@@ -73679,7 +75483,7 @@
         <v>0.77777777777777779</v>
       </c>
     </row>
-    <row r="122" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1276</v>
       </c>
@@ -73987,7 +75791,7 @@
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>1287</v>
       </c>
@@ -74274,7 +76078,7 @@
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="124" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1298</v>
       </c>
@@ -74555,7 +76359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1309</v>
       </c>
@@ -74851,7 +76655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1320</v>
       </c>
@@ -75162,7 +76966,7 @@
         <v>0.69230769230769229</v>
       </c>
     </row>
-    <row r="127" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>1331</v>
       </c>
@@ -75431,7 +77235,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1340</v>
       </c>
@@ -75718,7 +77522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>1351</v>
       </c>
@@ -76032,7 +77836,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="130" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1362</v>
       </c>
@@ -76277,7 +78081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1373</v>
       </c>
@@ -76588,7 +78392,7 @@
         <v>0.61538461538461542</v>
       </c>
     </row>
-    <row r="132" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1384</v>
       </c>
@@ -76911,7 +78715,7 @@
         <v>0.5636363636363636</v>
       </c>
     </row>
-    <row r="133" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1395</v>
       </c>
@@ -77207,7 +79011,7 @@
         <v>0.27272727272727271</v>
       </c>
     </row>
-    <row r="134" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1406</v>
       </c>
@@ -77491,7 +79295,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="135" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1416</v>
       </c>
